--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/01_CMG1 - APQP, Fizibilite ve Kaynaklar/EKG-PRJ-FRM-25_otomotiv_cami_apqp_formlari__birlesik_calisma_kitabi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/01_CMG1 - APQP, Fizibilite ve Kaynaklar/EKG-PRJ-FRM-25_otomotiv_cami_apqp_formlari__birlesik_calisma_kitabi.xlsx
@@ -1224,7 +1224,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-25&amp;C&amp;"Arial,Regular"&amp;11Otomotiv Camı APQP Formları - Birleşik Çalışma Kitabı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kanıtsız fizibilite cevapları kaldırıldı; PFMEA, karakteristik ve kontrol planı şablonları düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1358,7 +1359,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-25&amp;C&amp;"Arial,Regular"&amp;11Otomotiv Camı APQP Formları - Birleşik Çalışma Kitabı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kanıtsız fizibilite cevapları kaldırıldı; PFMEA, karakteristik ve kontrol planı şablonları düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1528,7 +1530,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-25&amp;C&amp;"Arial,Regular"&amp;11Otomotiv Camı APQP Formları - Birleşik Çalışma Kitabı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kanıtsız fizibilite cevapları kaldırıldı; PFMEA, karakteristik ve kontrol planı şablonları düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1686,7 +1689,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-25&amp;C&amp;"Arial,Regular"&amp;11Otomotiv Camı APQP Formları - Birleşik Çalışma Kitabı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kanıtsız fizibilite cevapları kaldırıldı; PFMEA, karakteristik ve kontrol planı şablonları düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1873,7 +1877,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-25&amp;C&amp;"Arial,Regular"&amp;11Otomotiv Camı APQP Formları - Birleşik Çalışma Kitabı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Kanıtsız fizibilite cevapları kaldırıldı; PFMEA, karakteristik ve kontrol planı şablonları düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>